--- a/backend/src/sources/static/worker_safety/worker_safety_2020-2024.xlsx
+++ b/backend/src/sources/static/worker_safety/worker_safety_2020-2024.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Forespørgsler\2025\Eksterne\Privatperson - Aleksander Bang-Larsen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEEE72D9-2A2D-4F3E-9FAC-ED6BB3DF0F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E959EE8A-864D-4D6D-B38B-45644B3CEE65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{DB742CCE-04A5-4145-8458-AC8892D852A9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{DB742CCE-04A5-4145-8458-AC8892D852A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Landbrug mv" sheetId="4" r:id="rId1"/>
+    <sheet name="Skadeart" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Landbrug mv'!$B$3:$G$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Skadeart!$A$3:$I$96</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="21">
   <si>
     <t>I alt</t>
   </si>
@@ -57,6 +59,51 @@
   </si>
   <si>
     <t>Anmeldte ulykker i EASY med mere end én dags fravær i branchegruppen "Landbrug, jagt, skovbrug og fiskeri" 2020-2024 - fordelt på CVR-nummer</t>
+  </si>
+  <si>
+    <t>Lukkede brud</t>
+  </si>
+  <si>
+    <t>Forstuvninger og forstrækninger (inkl. overrivning af muskler, sener/nerver, brok)</t>
+  </si>
+  <si>
+    <t>Andre former for ledskred, forstuvninger og forstrækninger</t>
+  </si>
+  <si>
+    <t>Åbne sår (inkl. afrivning af negle, sår med muskel-/sene-/nerveskader)</t>
+  </si>
+  <si>
+    <t>Anden oplyst skade</t>
+  </si>
+  <si>
+    <t>Hjernerystelse og indre skader i kraniet</t>
+  </si>
+  <si>
+    <t>Flere lige alvorlige skader</t>
+  </si>
+  <si>
+    <t>Akut infektion</t>
+  </si>
+  <si>
+    <t>Overfladiske skader (inkl. blå mærker, insektbid, fremmedlegme i øje eller øre)</t>
+  </si>
+  <si>
+    <t>Andre former for sår og overfladiske skader</t>
+  </si>
+  <si>
+    <t>Uoplyst skade</t>
+  </si>
+  <si>
+    <t>Ledskred (fx skulder der er gået af led)</t>
+  </si>
+  <si>
+    <t>Andre former for forgiftning og infektion</t>
+  </si>
+  <si>
+    <t>Skadeart</t>
+  </si>
+  <si>
+    <t>Anmeldte ulykker i EASY med mere end én dags fravær i branchegruppen "Landbrug, jagt, skovbrug og fiskeri" 2020-2024 - fordelt på CVR-nummer og skadeart</t>
   </si>
 </sst>
 </file>
@@ -96,7 +143,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -119,11 +166,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -157,6 +213,20 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5445,7 +5515,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:G195" xr:uid="{4FC59A81-8EAF-4C66-A95C-66EAA7D16950}"/>
   <mergeCells count="4">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:G2"/>
@@ -5454,4 +5523,2832 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D62B9596-DC21-43B2-859D-6097238612A2}">
+  <dimension ref="A1:I98"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="53.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+    </row>
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2021</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H3" s="1">
+        <v>2024</v>
+      </c>
+      <c r="I3" s="11"/>
+    </row>
+    <row r="4" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>27623549</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="17">
+        <v>13</v>
+      </c>
+      <c r="D4" s="17">
+        <v>8</v>
+      </c>
+      <c r="E4" s="17">
+        <v>9</v>
+      </c>
+      <c r="F4" s="17">
+        <v>11</v>
+      </c>
+      <c r="G4" s="17">
+        <v>15</v>
+      </c>
+      <c r="H4" s="17">
+        <v>18</v>
+      </c>
+      <c r="I4" s="17">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>35394818</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="17">
+        <v>11</v>
+      </c>
+      <c r="D5" s="17">
+        <v>11</v>
+      </c>
+      <c r="E5" s="17">
+        <v>5</v>
+      </c>
+      <c r="F5" s="17">
+        <v>16</v>
+      </c>
+      <c r="G5" s="17">
+        <v>13</v>
+      </c>
+      <c r="H5" s="17">
+        <v>17</v>
+      </c>
+      <c r="I5" s="17">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>35394818</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="17">
+        <v>8</v>
+      </c>
+      <c r="D6" s="17">
+        <v>12</v>
+      </c>
+      <c r="E6" s="17">
+        <v>6</v>
+      </c>
+      <c r="F6" s="17">
+        <v>10</v>
+      </c>
+      <c r="G6" s="17">
+        <v>10</v>
+      </c>
+      <c r="H6" s="17">
+        <v>5</v>
+      </c>
+      <c r="I6" s="17">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>35394818</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="17">
+        <v>6</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="17">
+        <v>6</v>
+      </c>
+      <c r="H7" s="17">
+        <v>9</v>
+      </c>
+      <c r="I7" s="17">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>27623549</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="17">
+        <v>6</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" s="17">
+        <v>8</v>
+      </c>
+      <c r="H8" s="17">
+        <v>5</v>
+      </c>
+      <c r="I8" s="17">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>33157274</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="17">
+        <v>10</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="17">
+        <v>9</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" s="17">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>27623549</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="17">
+        <v>5</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="17">
+        <v>8</v>
+      </c>
+      <c r="G10" s="17">
+        <v>6</v>
+      </c>
+      <c r="H10" s="17">
+        <v>5</v>
+      </c>
+      <c r="I10" s="17">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>29615756</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="17">
+        <v>8</v>
+      </c>
+      <c r="D11" s="17">
+        <v>8</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" s="17">
+        <v>7</v>
+      </c>
+      <c r="I11" s="17">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>35394818</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="17">
+        <v>7</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="17">
+        <v>5</v>
+      </c>
+      <c r="G12" s="17">
+        <v>5</v>
+      </c>
+      <c r="H12" s="17">
+        <v>7</v>
+      </c>
+      <c r="I12" s="17">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>27623549</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="17">
+        <v>6</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="17">
+        <v>12</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" s="17">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>29615756</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="17">
+        <v>5</v>
+      </c>
+      <c r="G14" s="17">
+        <v>7</v>
+      </c>
+      <c r="H14" s="17">
+        <v>6</v>
+      </c>
+      <c r="I14" s="17">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>64942212</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="17">
+        <v>5</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="17">
+        <v>5</v>
+      </c>
+      <c r="H15" s="17">
+        <v>6</v>
+      </c>
+      <c r="I15" s="17">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>35394818</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" s="17">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>32441483</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" s="17">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>26112389</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18" s="17">
+        <v>11</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I18" s="17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>62556013</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="17">
+        <v>14</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" s="17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>64942212</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" s="17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>35394818</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H21" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" s="17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>27623549</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" s="17">
+        <v>6</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" s="17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>27623549</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H23" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" s="17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>35418733</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H24" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I24" s="17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>27623549</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="17">
+        <v>7</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H25" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25" s="17">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>17514504</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H26" s="17">
+        <v>6</v>
+      </c>
+      <c r="I26" s="17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>28848609</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="17">
+        <v>12</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" s="17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>35394818</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="17">
+        <v>5</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H28" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I28" s="17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>25115279</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" s="17">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>31754615</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H30" s="17">
+        <v>5</v>
+      </c>
+      <c r="I30" s="17">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>33157274</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I31" s="17">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>17514504</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I32" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>19438414</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I33" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>27623549</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H34" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I34" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>31754615</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H35" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I35" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>31754615</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G36" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H36" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I36" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>31754615</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I37" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>33598653</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H38" s="17">
+        <v>5</v>
+      </c>
+      <c r="I38" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>35418733</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I39" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>66038319</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E40" s="17">
+        <v>5</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G40" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I40" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>74033911</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" s="17">
+        <v>5</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G41" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H41" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I41" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>29615756</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H42" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I42" s="17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>29615756</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G43" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H43" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I43" s="17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>32441483</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="17">
+        <v>5</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H44" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I44" s="17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>33598653</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G45" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H45" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I45" s="17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>15504749</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G46" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H46" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I46" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>21813095</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G47" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H47" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I47" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>29189498</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G48" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H48" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I48" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>29615756</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D49" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G49" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H49" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I49" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>31754615</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D50" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G50" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H50" s="17">
+        <v>6</v>
+      </c>
+      <c r="I50" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>19146847</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D51" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G51" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H51" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I51" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>19226980</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F52" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G52" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H52" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I52" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>19438414</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F53" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G53" s="17">
+        <v>5</v>
+      </c>
+      <c r="H53" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I53" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>25115279</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F54" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G54" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H54" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I54" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>27623549</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G55" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H55" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I55" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>27623549</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E56" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F56" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G56" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H56" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I56" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>29615756</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F57" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G57" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H57" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I57" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>33157274</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D58" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F58" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G58" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H58" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I58" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>33157274</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C59" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D59" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E59" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F59" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G59" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H59" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I59" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>35418733</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D60" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E60" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F60" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G60" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H60" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I60" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>40250441</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D61" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E61" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F61" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G61" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H61" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I61" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>52154413</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D62" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E62" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F62" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G62" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H62" s="17">
+        <v>6</v>
+      </c>
+      <c r="I62" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>64942212</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D63" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E63" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F63" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G63" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H63" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I63" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>64942212</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D64" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E64" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F64" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G64" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H64" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I64" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>66038319</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D65" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F65" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G65" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H65" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I65" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>17514504</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E66" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G66" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H66" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I66" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>19146847</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F67" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G67" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H67" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I67" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>19226980</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E68" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F68" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G68" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H68" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I68" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>21843148</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D69" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E69" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F69" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G69" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H69" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I69" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>26112389</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E70" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F70" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G70" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H70" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I70" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>26112389</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E71" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F71" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G71" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H71" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I71" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>27623549</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E72" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F72" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G72" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H72" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I72" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>35418733</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D73" s="17">
+        <v>5</v>
+      </c>
+      <c r="E73" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F73" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G73" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H73" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I73" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>52407915</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D74" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E74" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F74" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G74" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H74" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I74" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>65120119</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D75" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E75" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F75" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G75" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H75" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I75" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>10132851</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D76" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E76" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F76" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G76" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H76" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I76" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>12618735</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D77" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E77" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F77" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G77" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H77" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I77" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>13229848</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D78" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E78" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F78" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G78" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H78" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I78" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>15504749</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D79" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E79" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F79" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G79" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H79" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I79" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>19146847</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C80" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D80" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E80" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F80" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G80" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H80" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I80" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>25115279</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D81" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E81" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F81" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G81" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H81" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I81" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>27623549</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C82" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D82" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E82" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F82" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G82" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H82" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I82" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>27623549</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D83" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E83" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F83" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G83" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H83" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I83" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>27649661</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E84" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F84" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G84" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H84" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I84" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>29189498</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D85" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E85" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F85" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G85" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H85" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I85" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
+        <v>33157274</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D86" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E86" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F86" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G86" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H86" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I86" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
+        <v>35394818</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D87" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E87" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F87" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G87" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H87" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I87" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
+        <v>37622362</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D88" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E88" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F88" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G88" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H88" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I88" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
+        <v>62556013</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D89" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E89" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F89" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G89" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H89" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I89" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
+        <v>62556013</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D90" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E90" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F90" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G90" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H90" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I90" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
+        <v>62556013</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D91" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E91" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F91" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G91" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H91" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I91" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
+        <v>64942212</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D92" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E92" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F92" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G92" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H92" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I92" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A93" s="1">
+        <v>66038319</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D93" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E93" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F93" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G93" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H93" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I93" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
+        <v>73288312</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D94" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E94" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F94" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G94" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H94" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I94" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
+        <v>74033911</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D95" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E95" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F95" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G95" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H95" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I95" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
+        <v>75834128</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D96" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E96" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F96" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G96" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H96" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I96" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A97" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B97" s="16"/>
+      <c r="C97" s="15">
+        <v>875</v>
+      </c>
+      <c r="D97" s="15">
+        <v>1017</v>
+      </c>
+      <c r="E97" s="15">
+        <v>1089</v>
+      </c>
+      <c r="F97" s="15">
+        <v>1032</v>
+      </c>
+      <c r="G97" s="15">
+        <v>1130</v>
+      </c>
+      <c r="H97" s="15">
+        <v>1213</v>
+      </c>
+      <c r="I97" s="15">
+        <v>5723</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A98" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B98" s="14"/>
+      <c r="C98" s="13">
+        <v>950</v>
+      </c>
+      <c r="D98" s="13">
+        <v>1082</v>
+      </c>
+      <c r="E98" s="13">
+        <v>1171</v>
+      </c>
+      <c r="F98" s="13">
+        <v>1093</v>
+      </c>
+      <c r="G98" s="13">
+        <v>1222</v>
+      </c>
+      <c r="H98" s="13">
+        <v>1326</v>
+      </c>
+      <c r="I98" s="13">
+        <v>6844</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/backend/src/sources/static/worker_safety/worker_safety_2020-2024.xlsx
+++ b/backend/src/sources/static/worker_safety/worker_safety_2020-2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Forespørgsler\2025\Eksterne\Privatperson - Aleksander Bang-Larsen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aleksander/Tinker/landbruget.dk/backend/src/sources/static/worker_safety/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E959EE8A-864D-4D6D-B38B-45644B3CEE65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B0DF89-F6C5-FA4E-A648-B2EBDDB3F2C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{DB742CCE-04A5-4145-8458-AC8892D852A9}"/>
+    <workbookView xWindow="200" yWindow="700" windowWidth="31740" windowHeight="26120" xr2:uid="{DB742CCE-04A5-4145-8458-AC8892D852A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Landbrug mv" sheetId="4" r:id="rId1"/>
@@ -179,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -203,6 +203,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -212,23 +217,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -470,38 +474,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FC59A81-8EAF-4C66-A95C-66EAA7D16950}">
   <dimension ref="A1:H195"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+    <row r="1" spans="1:8" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B2" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.15">
+      <c r="A3" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="11" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="9"/>
       <c r="B3" s="8">
         <v>2019</v>
       </c>
@@ -520,9 +520,11 @@
       <c r="G3" s="8">
         <v>2024</v>
       </c>
-      <c r="H3" s="11"/>
-    </row>
-    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="H3" s="19" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>35394818</v>
       </c>
@@ -548,7 +550,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>27623549</v>
       </c>
@@ -574,7 +576,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>29615756</v>
       </c>
@@ -600,7 +602,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>64942212</v>
       </c>
@@ -626,7 +628,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>33157274</v>
       </c>
@@ -652,7 +654,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>31754615</v>
       </c>
@@ -678,7 +680,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>35418733</v>
       </c>
@@ -704,7 +706,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>17514504</v>
       </c>
@@ -730,7 +732,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>32441483</v>
       </c>
@@ -756,7 +758,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>25115279</v>
       </c>
@@ -782,7 +784,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>33598653</v>
       </c>
@@ -808,7 +810,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>62556013</v>
       </c>
@@ -834,7 +836,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>66038319</v>
       </c>
@@ -860,7 +862,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>26112389</v>
       </c>
@@ -886,7 +888,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>15504749</v>
       </c>
@@ -912,7 +914,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>19146847</v>
       </c>
@@ -938,7 +940,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>19226980</v>
       </c>
@@ -964,7 +966,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>19438414</v>
       </c>
@@ -990,7 +992,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>29189498</v>
       </c>
@@ -1016,7 +1018,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>74033911</v>
       </c>
@@ -1042,7 +1044,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>27649661</v>
       </c>
@@ -1068,7 +1070,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>41469633</v>
       </c>
@@ -1094,7 +1096,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>21813095</v>
       </c>
@@ -1120,7 +1122,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>31576601</v>
       </c>
@@ -1146,7 +1148,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>65120119</v>
       </c>
@@ -1172,7 +1174,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>10132851</v>
       </c>
@@ -1198,7 +1200,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>12618735</v>
       </c>
@@ -1224,7 +1226,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>27121578</v>
       </c>
@@ -1250,7 +1252,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>31379857</v>
       </c>
@@ -1276,7 +1278,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>32450938</v>
       </c>
@@ -1302,7 +1304,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>36465573</v>
       </c>
@@ -1328,7 +1330,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>36533471</v>
       </c>
@@ -1354,7 +1356,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>21806935</v>
       </c>
@@ -1380,7 +1382,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>14035370</v>
       </c>
@@ -1406,7 +1408,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>21351695</v>
       </c>
@@ -1432,7 +1434,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>28848609</v>
       </c>
@@ -1458,7 +1460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>73288312</v>
       </c>
@@ -1484,7 +1486,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>15692987</v>
       </c>
@@ -1510,7 +1512,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>40250441</v>
       </c>
@@ -1536,7 +1538,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>52844614</v>
       </c>
@@ -1562,7 +1564,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>78591617</v>
       </c>
@@ -1588,7 +1590,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>16165549</v>
       </c>
@@ -1614,7 +1616,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>33854293</v>
       </c>
@@ -1640,7 +1642,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>34596085</v>
       </c>
@@ -1666,7 +1668,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>37536911</v>
       </c>
@@ -1692,7 +1694,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>39117568</v>
       </c>
@@ -1718,7 +1720,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>52154413</v>
       </c>
@@ -1744,7 +1746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>10997801</v>
       </c>
@@ -1770,7 +1772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>15104716</v>
       </c>
@@ -1796,7 +1798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>25615085</v>
       </c>
@@ -1822,7 +1824,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>30186915</v>
       </c>
@@ -1848,7 +1850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>35630937</v>
       </c>
@@ -1874,7 +1876,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>38748351</v>
       </c>
@@ -1900,7 +1902,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>38755641</v>
       </c>
@@ -1926,7 +1928,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>73528119</v>
       </c>
@@ -1952,7 +1954,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>11757278</v>
       </c>
@@ -1978,7 +1980,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>17118439</v>
       </c>
@@ -2004,7 +2006,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>18653133</v>
       </c>
@@ -2030,7 +2032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>21843148</v>
       </c>
@@ -2056,7 +2058,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>27252389</v>
       </c>
@@ -2082,7 +2084,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>27723047</v>
       </c>
@@ -2108,7 +2110,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>29180636</v>
       </c>
@@ -2134,7 +2136,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>29953856</v>
       </c>
@@ -2160,7 +2162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>30323726</v>
       </c>
@@ -2186,7 +2188,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>35531297</v>
       </c>
@@ -2212,7 +2214,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>35683356</v>
       </c>
@@ -2238,7 +2240,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>36925655</v>
       </c>
@@ -2264,7 +2266,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>38381547</v>
       </c>
@@ -2290,7 +2292,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>52407915</v>
       </c>
@@ -2316,7 +2318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>65835916</v>
       </c>
@@ -2342,7 +2344,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>75834128</v>
       </c>
@@ -2368,7 +2370,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>11676901</v>
       </c>
@@ -2394,7 +2396,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>14943994</v>
       </c>
@@ -2420,7 +2422,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>21076139</v>
       </c>
@@ -2446,7 +2448,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>26085462</v>
       </c>
@@ -2472,7 +2474,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>26256909</v>
       </c>
@@ -2498,7 +2500,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>28261942</v>
       </c>
@@ -2524,7 +2526,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>29442703</v>
       </c>
@@ -2550,7 +2552,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>39668807</v>
       </c>
@@ -2576,7 +2578,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>40589287</v>
       </c>
@@ -2602,7 +2604,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>80326610</v>
       </c>
@@ -2628,7 +2630,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>17519107</v>
       </c>
@@ -2654,7 +2656,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>18336979</v>
       </c>
@@ -2680,7 +2682,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>21122092</v>
       </c>
@@ -2706,7 +2708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>25902025</v>
       </c>
@@ -2732,7 +2734,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>26028078</v>
       </c>
@@ -2758,7 +2760,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>29415153</v>
       </c>
@@ -2784,7 +2786,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>29737991</v>
       </c>
@@ -2810,7 +2812,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>30714415</v>
       </c>
@@ -2836,7 +2838,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>31757347</v>
       </c>
@@ -2862,7 +2864,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>32082432</v>
       </c>
@@ -2888,7 +2890,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>34364826</v>
       </c>
@@ -2914,7 +2916,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>34458413</v>
       </c>
@@ -2940,7 +2942,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>35385509</v>
       </c>
@@ -2966,7 +2968,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>39208024</v>
       </c>
@@ -2992,7 +2994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>39307774</v>
       </c>
@@ -3018,7 +3020,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>40323317</v>
       </c>
@@ -3044,7 +3046,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>59607316</v>
       </c>
@@ -3070,7 +3072,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>10504570</v>
       </c>
@@ -3096,7 +3098,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>12027435</v>
       </c>
@@ -3122,7 +3124,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>13170541</v>
       </c>
@@ -3148,7 +3150,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>13229848</v>
       </c>
@@ -3174,7 +3176,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>15520477</v>
       </c>
@@ -3200,7 +3202,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>16128872</v>
       </c>
@@ -3226,7 +3228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>17926101</v>
       </c>
@@ -3252,7 +3254,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>19286630</v>
       </c>
@@ -3278,7 +3280,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>20310413</v>
       </c>
@@ -3304,7 +3306,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>21507334</v>
       </c>
@@ -3330,7 +3332,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>25221184</v>
       </c>
@@ -3356,7 +3358,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>25707524</v>
       </c>
@@ -3382,7 +3384,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>25929403</v>
       </c>
@@ -3408,7 +3410,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>30069579</v>
       </c>
@@ -3434,7 +3436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>31798701</v>
       </c>
@@ -3460,7 +3462,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>33770642</v>
       </c>
@@ -3486,7 +3488,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>35051007</v>
       </c>
@@ -3512,7 +3514,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>36056428</v>
       </c>
@@ -3538,7 +3540,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>36604565</v>
       </c>
@@ -3564,7 +3566,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>37317969</v>
       </c>
@@ -3590,7 +3592,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
         <v>37832847</v>
       </c>
@@ -3616,7 +3618,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
         <v>38046543</v>
       </c>
@@ -3642,7 +3644,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
         <v>38070711</v>
       </c>
@@ -3668,7 +3670,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
         <v>38175386</v>
       </c>
@@ -3694,7 +3696,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
         <v>38847147</v>
       </c>
@@ -3720,7 +3722,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
         <v>38947737</v>
       </c>
@@ -3746,7 +3748,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
         <v>39329433</v>
       </c>
@@ -3772,7 +3774,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
         <v>40230785</v>
       </c>
@@ -3798,7 +3800,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
         <v>40577645</v>
       </c>
@@ -3824,7 +3826,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
         <v>40660933</v>
       </c>
@@ -3850,7 +3852,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
         <v>41800933</v>
       </c>
@@ -3876,7 +3878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
         <v>57020415</v>
       </c>
@@ -3902,7 +3904,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
         <v>68473616</v>
       </c>
@@ -3928,7 +3930,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
         <v>79538310</v>
       </c>
@@ -3954,7 +3956,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
         <v>89649617</v>
       </c>
@@ -3980,7 +3982,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
         <v>12255373</v>
       </c>
@@ -4006,7 +4008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
         <v>12853580</v>
       </c>
@@ -4032,7 +4034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
         <v>13087806</v>
       </c>
@@ -4058,7 +4060,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>17055682</v>
       </c>
@@ -4084,7 +4086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>17242342</v>
       </c>
@@ -4110,7 +4112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>17631047</v>
       </c>
@@ -4136,7 +4138,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>18091097</v>
       </c>
@@ -4162,7 +4164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>19605280</v>
       </c>
@@ -4188,7 +4190,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>20500794</v>
       </c>
@@ -4214,7 +4216,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>20971134</v>
       </c>
@@ -4240,7 +4242,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>21201146</v>
       </c>
@@ -4266,7 +4268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>21291072</v>
       </c>
@@ -4292,7 +4294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>25025091</v>
       </c>
@@ -4318,7 +4320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>25061918</v>
       </c>
@@ -4344,7 +4346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
         <v>25085027</v>
       </c>
@@ -4370,7 +4372,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
         <v>25085892</v>
       </c>
@@ -4396,7 +4398,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
         <v>25188012</v>
       </c>
@@ -4422,7 +4424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
         <v>25319680</v>
       </c>
@@ -4448,7 +4450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
         <v>25931416</v>
       </c>
@@ -4474,7 +4476,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
         <v>26091063</v>
       </c>
@@ -4500,7 +4502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
         <v>27209270</v>
       </c>
@@ -4526,7 +4528,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
         <v>27614264</v>
       </c>
@@ -4552,7 +4554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
         <v>27674534</v>
       </c>
@@ -4578,7 +4580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
         <v>27840108</v>
       </c>
@@ -4604,7 +4606,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
         <v>28030002</v>
       </c>
@@ -4630,7 +4632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
         <v>28328532</v>
       </c>
@@ -4656,7 +4658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
         <v>28864353</v>
       </c>
@@ -4682,7 +4684,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
         <v>29243298</v>
       </c>
@@ -4708,7 +4710,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
         <v>29409498</v>
       </c>
@@ -4734,7 +4736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
         <v>30884663</v>
       </c>
@@ -4760,7 +4762,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
         <v>31418860</v>
       </c>
@@ -4786,7 +4788,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
         <v>31564085</v>
       </c>
@@ -4812,7 +4814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
         <v>31582091</v>
       </c>
@@ -4838,7 +4840,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
         <v>31719062</v>
       </c>
@@ -4864,7 +4866,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
         <v>32261868</v>
       </c>
@@ -4890,7 +4892,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
         <v>33178808</v>
       </c>
@@ -4916,7 +4918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
         <v>33303599</v>
       </c>
@@ -4942,7 +4944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
         <v>33660650</v>
       </c>
@@ -4968,7 +4970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
         <v>34734100</v>
       </c>
@@ -4994,7 +4996,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
         <v>34947015</v>
       </c>
@@ -5020,7 +5022,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
         <v>35600345</v>
       </c>
@@ -5046,7 +5048,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
         <v>37313998</v>
       </c>
@@ -5072,7 +5074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
         <v>37506001</v>
       </c>
@@ -5098,7 +5100,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
         <v>37622362</v>
       </c>
@@ -5124,7 +5126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
         <v>38097512</v>
       </c>
@@ -5150,7 +5152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
         <v>39196220</v>
       </c>
@@ -5176,7 +5178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
         <v>40097813</v>
       </c>
@@ -5202,7 +5204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
         <v>40338209</v>
       </c>
@@ -5228,7 +5230,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
         <v>40398325</v>
       </c>
@@ -5254,7 +5256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
         <v>41173475</v>
       </c>
@@ -5280,7 +5282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
         <v>42686913</v>
       </c>
@@ -5306,7 +5308,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
         <v>59108115</v>
       </c>
@@ -5332,7 +5334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
         <v>59561510</v>
       </c>
@@ -5358,7 +5360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
         <v>70817128</v>
       </c>
@@ -5384,7 +5386,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
         <v>72366018</v>
       </c>
@@ -5410,7 +5412,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
         <v>77027211</v>
       </c>
@@ -5436,7 +5438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
         <v>84249610</v>
       </c>
@@ -5462,7 +5464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A194" s="3" t="s">
         <v>1</v>
       </c>
@@ -5488,7 +5490,7 @@
         <v>4170</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:8" ht="15" x14ac:dyDescent="0.15">
       <c r="A195" s="2" t="s">
         <v>0</v>
       </c>
@@ -5515,59 +5517,57 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A2:A3"/>
+  <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D62B9596-DC21-43B2-859D-6097238612A2}">
   <dimension ref="A1:I98"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="53.25" customWidth="1"/>
+    <col min="2" max="2" width="53.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-    </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+    </row>
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="11" t="s">
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
       <c r="C3" s="1">
         <v>2019</v>
       </c>
@@ -5586,2756 +5586,2756 @@
       <c r="H3" s="1">
         <v>2024</v>
       </c>
-      <c r="I3" s="11"/>
-    </row>
-    <row r="4" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I3" s="14"/>
+    </row>
+    <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>27623549</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="11">
         <v>13</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="11">
         <v>8</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="11">
         <v>9</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="11">
         <v>11</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="11">
         <v>15</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="11">
         <v>18</v>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="11">
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>35394818</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="11">
         <v>11</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="11">
         <v>11</v>
       </c>
-      <c r="E5" s="17">
-        <v>5</v>
-      </c>
-      <c r="F5" s="17">
+      <c r="E5" s="11">
+        <v>5</v>
+      </c>
+      <c r="F5" s="11">
         <v>16</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="11">
         <v>13</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="11">
         <v>17</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="11">
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>35394818</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="11">
         <v>8</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="11">
         <v>12</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="11">
         <v>6</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="11">
         <v>10</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="11">
         <v>10</v>
       </c>
-      <c r="H6" s="17">
-        <v>5</v>
-      </c>
-      <c r="I6" s="17">
+      <c r="H6" s="11">
+        <v>5</v>
+      </c>
+      <c r="I6" s="11">
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>35394818</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="11">
         <v>6</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G7" s="17">
+      <c r="D7" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="11">
         <v>6</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="11">
         <v>9</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="11">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>27623549</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="17">
+      <c r="C8" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="11">
         <v>6</v>
       </c>
-      <c r="E8" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G8" s="17">
+      <c r="E8" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" s="11">
         <v>8</v>
       </c>
-      <c r="H8" s="17">
-        <v>5</v>
-      </c>
-      <c r="I8" s="17">
+      <c r="H8" s="11">
+        <v>5</v>
+      </c>
+      <c r="I8" s="11">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>33157274</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="11">
         <v>10</v>
       </c>
-      <c r="D9" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="17">
+      <c r="D9" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="11">
         <v>9</v>
       </c>
-      <c r="F9" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I9" s="17">
+      <c r="F9" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" s="11">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>27623549</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="17">
-        <v>5</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F10" s="17">
+      <c r="C10" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="11">
+        <v>5</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="11">
         <v>8</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="11">
         <v>6</v>
       </c>
-      <c r="H10" s="17">
-        <v>5</v>
-      </c>
-      <c r="I10" s="17">
+      <c r="H10" s="11">
+        <v>5</v>
+      </c>
+      <c r="I10" s="11">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>29615756</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="11">
         <v>8</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="11">
         <v>8</v>
       </c>
-      <c r="E11" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H11" s="17">
+      <c r="E11" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" s="11">
         <v>7</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="11">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>35394818</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="11">
         <v>7</v>
       </c>
-      <c r="D12" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F12" s="17">
-        <v>5</v>
-      </c>
-      <c r="G12" s="17">
-        <v>5</v>
-      </c>
-      <c r="H12" s="17">
+      <c r="D12" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="11">
+        <v>5</v>
+      </c>
+      <c r="G12" s="11">
+        <v>5</v>
+      </c>
+      <c r="H12" s="11">
         <v>7</v>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="11">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>27623549</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" s="17">
+      <c r="C13" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="11">
         <v>6</v>
       </c>
-      <c r="F13" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G13" s="17">
+      <c r="F13" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="11">
         <v>12</v>
       </c>
-      <c r="H13" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I13" s="17">
+      <c r="H13" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" s="11">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>29615756</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F14" s="17">
-        <v>5</v>
-      </c>
-      <c r="G14" s="17">
+      <c r="C14" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="11">
+        <v>5</v>
+      </c>
+      <c r="G14" s="11">
         <v>7</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="11">
         <v>6</v>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="11">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>64942212</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="17">
-        <v>5</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G15" s="17">
-        <v>5</v>
-      </c>
-      <c r="H15" s="17">
+      <c r="C15" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="11">
+        <v>5</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="11">
+        <v>5</v>
+      </c>
+      <c r="H15" s="11">
         <v>6</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="11">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>35394818</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I16" s="17">
+      <c r="C16" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" s="11">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>32441483</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H17" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I17" s="17">
+      <c r="C17" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" s="11">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>26112389</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E18" s="17">
+      <c r="C18" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18" s="11">
         <v>11</v>
       </c>
-      <c r="F18" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I18" s="17">
+      <c r="F18" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I18" s="11">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>62556013</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E19" s="17">
+      <c r="C19" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="11">
         <v>14</v>
       </c>
-      <c r="F19" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I19" s="17">
+      <c r="F19" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" s="11">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>64942212</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I20" s="17">
+      <c r="C20" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" s="11">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>35394818</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H21" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I21" s="17">
+      <c r="C21" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" s="11">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>27623549</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F22" s="17">
+      <c r="C22" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" s="11">
         <v>6</v>
       </c>
-      <c r="G22" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I22" s="17">
+      <c r="G22" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" s="11">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>27623549</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H23" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I23" s="17">
+      <c r="C23" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" s="11">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>35418733</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C24" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H24" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I24" s="17">
+      <c r="C24" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I24" s="11">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>27623549</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="11">
         <v>7</v>
       </c>
-      <c r="D25" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H25" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I25" s="17">
+      <c r="D25" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25" s="11">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>17514504</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H26" s="17">
+      <c r="C26" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H26" s="11">
         <v>6</v>
       </c>
-      <c r="I26" s="17">
+      <c r="I26" s="11">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>28848609</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27" s="17">
+      <c r="C27" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="11">
         <v>12</v>
       </c>
-      <c r="F27" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G27" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H27" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I27" s="17">
+      <c r="F27" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" s="11">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>35394818</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E28" s="17">
-        <v>5</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H28" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I28" s="17">
+      <c r="C28" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="11">
+        <v>5</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I28" s="11">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>25115279</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G29" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H29" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I29" s="17">
+      <c r="C29" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" s="11">
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>31754615</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F30" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G30" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H30" s="17">
-        <v>5</v>
-      </c>
-      <c r="I30" s="17">
+      <c r="C30" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H30" s="11">
+        <v>5</v>
+      </c>
+      <c r="I30" s="11">
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>33157274</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H31" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I31" s="17">
+      <c r="C31" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I31" s="11">
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>17514504</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F32" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G32" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I32" s="17">
+      <c r="C32" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I32" s="11">
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>19438414</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F33" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G33" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H33" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I33" s="17">
+      <c r="C33" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I33" s="11">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>27623549</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C34" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F34" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G34" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I34" s="17">
+      <c r="C34" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I34" s="11">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>31754615</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D35" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F35" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G35" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H35" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I35" s="17">
+      <c r="C35" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I35" s="11">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>31754615</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F36" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G36" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H36" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I36" s="17">
+      <c r="C36" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I36" s="11">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>31754615</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F37" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G37" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H37" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I37" s="17">
+      <c r="C37" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I37" s="11">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>33598653</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D38" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F38" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G38" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H38" s="17">
-        <v>5</v>
-      </c>
-      <c r="I38" s="17">
+      <c r="C38" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H38" s="11">
+        <v>5</v>
+      </c>
+      <c r="I38" s="11">
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>35418733</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D39" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F39" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H39" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I39" s="17">
+      <c r="C39" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I39" s="11">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>66038319</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D40" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E40" s="17">
-        <v>5</v>
-      </c>
-      <c r="F40" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G40" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H40" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I40" s="17">
+      <c r="C40" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E40" s="11">
+        <v>5</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I40" s="11">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>74033911</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C41" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D41" s="17">
-        <v>5</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F41" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G41" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H41" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I41" s="17">
+      <c r="C41" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" s="11">
+        <v>5</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I41" s="11">
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>29615756</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C42" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E42" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F42" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G42" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H42" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I42" s="17">
+      <c r="C42" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I42" s="11">
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>29615756</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C43" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D43" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E43" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F43" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G43" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H43" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I43" s="17">
+      <c r="C43" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I43" s="11">
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>32441483</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="17">
-        <v>5</v>
-      </c>
-      <c r="D44" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E44" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F44" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G44" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H44" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I44" s="17">
+      <c r="C44" s="11">
+        <v>5</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I44" s="11">
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>33598653</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D45" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E45" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F45" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G45" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H45" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I45" s="17">
+      <c r="C45" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I45" s="11">
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>15504749</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C46" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D46" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E46" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F46" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G46" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H46" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I46" s="17">
+      <c r="C46" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I46" s="11">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>21813095</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C47" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D47" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E47" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F47" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G47" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H47" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I47" s="17">
+      <c r="C47" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I47" s="11">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>29189498</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E48" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F48" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G48" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H48" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I48" s="17">
+      <c r="C48" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I48" s="11">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>29615756</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E49" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F49" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G49" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H49" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I49" s="17">
+      <c r="C49" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I49" s="11">
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>31754615</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C50" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D50" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E50" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F50" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G50" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H50" s="17">
+      <c r="C50" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H50" s="11">
         <v>6</v>
       </c>
-      <c r="I50" s="17">
+      <c r="I50" s="11">
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>19146847</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C51" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D51" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E51" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F51" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G51" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H51" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I51" s="17">
+      <c r="C51" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I51" s="11">
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>19226980</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C52" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D52" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F52" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G52" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H52" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I52" s="17">
+      <c r="C52" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H52" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I52" s="11">
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>19438414</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D53" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E53" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F53" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G53" s="17">
-        <v>5</v>
-      </c>
-      <c r="H53" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I53" s="17">
+      <c r="C53" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G53" s="11">
+        <v>5</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I53" s="11">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>25115279</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C54" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D54" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E54" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F54" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G54" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H54" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I54" s="17">
+      <c r="C54" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I54" s="11">
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>27623549</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C55" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D55" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E55" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F55" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G55" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H55" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I55" s="17">
+      <c r="C55" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I55" s="11">
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>27623549</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C56" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D56" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E56" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F56" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G56" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H56" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I56" s="17">
+      <c r="C56" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G56" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I56" s="11">
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>29615756</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C57" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D57" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E57" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F57" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G57" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H57" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I57" s="17">
+      <c r="C57" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I57" s="11">
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>33157274</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C58" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D58" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E58" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F58" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G58" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H58" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I58" s="17">
+      <c r="C58" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G58" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I58" s="11">
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>33157274</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C59" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D59" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E59" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F59" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G59" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H59" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I59" s="17">
+      <c r="C59" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I59" s="11">
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>35418733</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C60" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D60" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E60" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F60" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G60" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H60" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I60" s="17">
+      <c r="C60" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G60" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H60" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I60" s="11">
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>40250441</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C61" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D61" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E61" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F61" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G61" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H61" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I61" s="17">
+      <c r="C61" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G61" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H61" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I61" s="11">
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>52154413</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C62" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D62" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E62" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F62" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G62" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H62" s="17">
+      <c r="C62" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G62" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H62" s="11">
         <v>6</v>
       </c>
-      <c r="I62" s="17">
+      <c r="I62" s="11">
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>64942212</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C63" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D63" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E63" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F63" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G63" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H63" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I63" s="17">
+      <c r="C63" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G63" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H63" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I63" s="11">
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>64942212</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C64" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D64" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E64" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F64" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G64" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H64" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I64" s="17">
+      <c r="C64" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G64" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H64" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I64" s="11">
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>66038319</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D65" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E65" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F65" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G65" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H65" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I65" s="17">
+      <c r="C65" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G65" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I65" s="11">
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>17514504</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C66" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D66" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E66" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F66" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G66" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H66" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I66" s="17">
+      <c r="C66" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I66" s="11">
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>19146847</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C67" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D67" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E67" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F67" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G67" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H67" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I67" s="17">
+      <c r="C67" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G67" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H67" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I67" s="11">
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>19226980</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C68" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D68" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E68" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F68" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G68" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H68" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I68" s="17">
+      <c r="C68" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G68" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H68" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I68" s="11">
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>21843148</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C69" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D69" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E69" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F69" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G69" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H69" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I69" s="17">
+      <c r="C69" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G69" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H69" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I69" s="11">
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>26112389</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D70" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E70" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F70" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G70" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H70" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I70" s="17">
+      <c r="C70" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F70" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G70" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H70" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I70" s="11">
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>26112389</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C71" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D71" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E71" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F71" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G71" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H71" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I71" s="17">
+      <c r="C71" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H71" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I71" s="11">
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>27623549</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C72" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D72" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E72" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F72" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G72" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H72" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I72" s="17">
+      <c r="C72" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F72" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G72" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H72" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I72" s="11">
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>35418733</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C73" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D73" s="17">
-        <v>5</v>
-      </c>
-      <c r="E73" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F73" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G73" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H73" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I73" s="17">
+      <c r="C73" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D73" s="11">
+        <v>5</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H73" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I73" s="11">
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>52407915</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C74" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D74" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E74" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F74" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G74" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H74" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I74" s="17">
+      <c r="C74" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G74" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H74" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I74" s="11">
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>65120119</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C75" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D75" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E75" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F75" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G75" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H75" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I75" s="17">
+      <c r="C75" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G75" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H75" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I75" s="11">
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>10132851</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D76" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E76" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F76" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G76" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H76" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I76" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C76" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G76" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H76" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I76" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>12618735</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C77" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D77" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E77" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F77" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G77" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H77" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I77" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="C77" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F77" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G77" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H77" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I77" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>13229848</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C78" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D78" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E78" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F78" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G78" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H78" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I78" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C78" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F78" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H78" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I78" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>15504749</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C79" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D79" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E79" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F79" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G79" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H79" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I79" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="C79" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F79" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H79" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I79" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>19146847</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C80" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D80" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E80" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F80" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G80" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H80" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I80" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="C80" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F80" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G80" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H80" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I80" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>25115279</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C81" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D81" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E81" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F81" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G81" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H81" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I81" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C81" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E81" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F81" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G81" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H81" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I81" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>27623549</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C82" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D82" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E82" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F82" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G82" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H82" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I82" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C82" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E82" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F82" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G82" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H82" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I82" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>27623549</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C83" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D83" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E83" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F83" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G83" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H83" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I83" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C83" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F83" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H83" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I83" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>27649661</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C84" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D84" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E84" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F84" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G84" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H84" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I84" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C84" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E84" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F84" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G84" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H84" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I84" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>29189498</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C85" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D85" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E85" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F85" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G85" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H85" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I85" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C85" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E85" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F85" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G85" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H85" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I85" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>33157274</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C86" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D86" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E86" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F86" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G86" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H86" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I86" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C86" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E86" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F86" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G86" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H86" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I86" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>35394818</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D87" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E87" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F87" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G87" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H87" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I87" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C87" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E87" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F87" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G87" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H87" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I87" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>37622362</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C88" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D88" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E88" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F88" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G88" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H88" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I88" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="C88" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E88" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F88" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G88" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H88" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I88" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>62556013</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C89" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D89" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E89" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F89" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G89" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H89" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I89" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C89" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D89" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E89" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F89" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G89" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H89" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I89" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>62556013</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C90" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D90" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E90" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F90" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G90" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H90" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I90" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="C90" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E90" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F90" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G90" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H90" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I90" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>62556013</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C91" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D91" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E91" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F91" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G91" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H91" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I91" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C91" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D91" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E91" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F91" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G91" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H91" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I91" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>64942212</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C92" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D92" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E92" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F92" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G92" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H92" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I92" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="C92" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E92" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F92" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G92" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H92" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I92" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>66038319</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C93" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D93" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E93" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F93" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G93" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H93" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I93" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C93" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D93" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E93" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F93" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G93" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H93" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I93" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>73288312</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C94" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D94" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E94" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F94" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G94" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H94" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I94" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="C94" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D94" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E94" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F94" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G94" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H94" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I94" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="30" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>74033911</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C95" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D95" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E95" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F95" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G95" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H95" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I95" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C95" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D95" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E95" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F95" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G95" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H95" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I95" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="15" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>75834128</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C96" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D96" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E96" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F96" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G96" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="H96" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="I96" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C96" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D96" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E96" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F96" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G96" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H96" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I96" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A97" s="16" t="s">
         <v>1</v>
       </c>
       <c r="B97" s="16"/>
-      <c r="C97" s="15">
+      <c r="C97" s="10">
         <v>875</v>
       </c>
-      <c r="D97" s="15">
+      <c r="D97" s="10">
         <v>1017</v>
       </c>
-      <c r="E97" s="15">
+      <c r="E97" s="10">
         <v>1089</v>
       </c>
-      <c r="F97" s="15">
+      <c r="F97" s="10">
         <v>1032</v>
       </c>
-      <c r="G97" s="15">
+      <c r="G97" s="10">
         <v>1130</v>
       </c>
-      <c r="H97" s="15">
+      <c r="H97" s="10">
         <v>1213</v>
       </c>
-      <c r="I97" s="15">
+      <c r="I97" s="10">
         <v>5723</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A98" s="14" t="s">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A98" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B98" s="14"/>
-      <c r="C98" s="13">
+      <c r="B98" s="17"/>
+      <c r="C98" s="9">
         <v>950</v>
       </c>
-      <c r="D98" s="13">
+      <c r="D98" s="9">
         <v>1082</v>
       </c>
-      <c r="E98" s="13">
+      <c r="E98" s="9">
         <v>1171</v>
       </c>
-      <c r="F98" s="13">
+      <c r="F98" s="9">
         <v>1093</v>
       </c>
-      <c r="G98" s="13">
+      <c r="G98" s="9">
         <v>1222</v>
       </c>
-      <c r="H98" s="13">
+      <c r="H98" s="9">
         <v>1326</v>
       </c>
-      <c r="I98" s="13">
+      <c r="I98" s="9">
         <v>6844</v>
       </c>
     </row>
